--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/01 18:43:40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-10</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>-10</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>-10</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,32 +75,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -110,190 +110,232 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>-22</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>9978</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1239.13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>-22</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1239.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -85,7 +85,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,32 +117,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -152,190 +152,232 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>9978</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1239.13</t>
+          <t>19978</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2574.44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1239.13</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2574.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -127,7 +127,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,32 +159,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -194,190 +194,232 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19978</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2574.44</t>
+          <t>29978</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3909.75</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2574.44</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3909.75</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 15:00:51</t>
+          <t>07/17 15:05:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1335.31</t>
+          <t>133.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -169,7 +169,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,32 +201,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -236,190 +236,232 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>29978</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3909.75</t>
+          <t>30978</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4043.48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3909.75</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4043.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 15:05:42</t>
+          <t>07/25 11:52:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 15:00:51</t>
+          <t>07/17 15:05:42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1335.31</t>
+          <t>133.73</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -211,7 +211,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,32 +243,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -278,190 +278,232 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>30978</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4043.48</t>
+          <t>33391.96</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4365.82</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>4043.48</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4365.82</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 11:52:03</t>
+          <t>07/25 11:52:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -85,17 +85,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>322.34</t>
+          <t>358.69</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 15:05:42</t>
+          <t>07/25 11:52:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 15:00:51</t>
+          <t>07/17 15:05:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1335.31</t>
+          <t>133.73</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -253,7 +253,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,32 +285,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -320,190 +320,232 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>33391.96</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4365.82</t>
+          <t>35805.93</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4724.51</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>4365.82</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4724.51</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 11:52:39</t>
+          <t>07/25 11:52:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>358.69</t>
+          <t>3030.91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 11:52:03</t>
+          <t>07/25 11:52:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -127,17 +127,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>322.34</t>
+          <t>358.69</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 15:05:42</t>
+          <t>07/25 11:52:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 15:00:51</t>
+          <t>07/17 15:05:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1335.31</t>
+          <t>133.73</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -295,7 +295,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,32 +327,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -362,190 +362,232 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>35805.93</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4724.51</t>
+          <t>56203.93</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7755.41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>4724.51</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>7755.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 11:52:52</t>
+          <t>07/25 12:23:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3030.91</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 11:52:39</t>
+          <t>07/25 11:52:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>358.69</t>
+          <t>3030.91</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 11:52:03</t>
+          <t>07/25 11:52:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -169,17 +169,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>322.34</t>
+          <t>358.69</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 15:05:42</t>
+          <t>07/25 11:52:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 15:00:51</t>
+          <t>07/17 15:05:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1335.31</t>
+          <t>133.73</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -337,7 +337,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,32 +369,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -404,190 +404,232 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>56203.93</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7755.41</t>
+          <t>57203.93</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7880.41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>7755.41</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7880.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 12:23:13</t>
+          <t>07/25 12:23:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 11:52:52</t>
+          <t>07/25 12:23:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3030.91</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 11:52:39</t>
+          <t>07/25 11:52:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>358.69</t>
+          <t>3030.91</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/25 11:52:03</t>
+          <t>07/25 11:52:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -211,17 +211,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>322.34</t>
+          <t>358.69</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 15:05:42</t>
+          <t>07/25 11:52:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 15:00:51</t>
+          <t>07/17 15:05:42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1335.31</t>
+          <t>133.73</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -379,7 +379,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,32 +411,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -446,190 +446,232 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>57203.93</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7880.41</t>
+          <t>77601.93</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10294.38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>7880.41</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10294.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 12:23:21</t>
+          <t>07/25 12:24:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 12:23:13</t>
+          <t>07/25 12:23:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 11:52:52</t>
+          <t>07/25 12:23:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3030.91</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/25 11:52:39</t>
+          <t>07/25 11:52:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>358.69</t>
+          <t>3030.91</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/25 11:52:03</t>
+          <t>07/25 11:52:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -253,17 +253,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>322.34</t>
+          <t>358.69</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 15:05:42</t>
+          <t>07/25 11:52:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 15:00:51</t>
+          <t>07/17 15:05:42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1335.31</t>
+          <t>133.73</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -421,7 +421,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,32 +453,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -488,190 +488,232 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>77601.93</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10294.38</t>
+          <t>97999.93</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12638.98</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>10294.38</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12638.98</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
+++ b/bills/JXZFSP/6897265765/8402300b7faba309d4fc835e41fb1b49e7d34c82f687bf472390dff0395f79f4/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 12:24:54</t>
+          <t>07/25 13:06:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 12:23:21</t>
+          <t>07/25 12:24:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 12:23:13</t>
+          <t>07/25 12:23:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/25 11:52:52</t>
+          <t>07/25 12:23:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3030.91</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/25 11:52:39</t>
+          <t>07/25 11:52:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2413.96</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>358.69</t>
+          <t>3030.91</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/25 11:52:03</t>
+          <t>07/25 11:52:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -295,17 +295,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>322.34</t>
+          <t>358.69</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 15:05:42</t>
+          <t>07/25 11:52:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2413.96</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>133.73</t>
+          <t>322.34</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/15 15:00:51</t>
+          <t>07/17 15:05:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1335.31</t>
+          <t>133.73</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/15 14:58:05</t>
+          <t>07/15 15:00:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/15 14:41:32</t>
+          <t>07/15 14:58:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1261.13</t>
+          <t>1335.31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,32 +495,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/03 20:48:38</t>
+          <t>07/15 14:41:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>1261.13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -530,190 +530,232 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/03 20:48:38</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>上海浦东新区 明天上午11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>17万 问</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/01 18:43:40</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>97999.93</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12638.98</t>
+          <t>118397.93</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14983.57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>12638.98</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14983.57</t>
         </is>
       </c>
     </row>
